--- a/registration_forms/004_podcast_platform_subscription_form--registration_forms.xlsx
+++ b/registration_forms/004_podcast_platform_subscription_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,8 +727,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -756,12 +756,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'free_trial'}</t>
+          <t>free_trial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Free Trial'}</t>
+          <t>Free Trial</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pro_monthly'}</t>
+          <t>pro_monthly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Pro Monthly'}</t>
+          <t>Pro Monthly</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'premium_quarterly'}</t>
+          <t>premium_quarterly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Premium Quarterly'}</t>
+          <t>Premium Quarterly</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'utc-0'}</t>
+          <t>utc-0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'UTC-0'}</t>
+          <t>UTC-0</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'utc-1'}</t>
+          <t>utc-1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'UTC-1'}</t>
+          <t>UTC-1</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'utc-2'}</t>
+          <t>utc-2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'UTC-2'}</t>
+          <t>UTC-2</t>
         </is>
       </c>
     </row>
